--- a/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>ICLK</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42825</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E8" s="3">
         <v>42600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>76300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>86800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>78000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>78700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>68900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>58100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>54200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>39200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>42600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>42700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>25900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E9" s="3">
         <v>81200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>65100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>53700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>55400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>48800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>41500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>35800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>35800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>33300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>32800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>30000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>22900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-38600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>2400</v>
+        <v>3300</v>
       </c>
       <c r="E12" s="3">
         <v>2400</v>
       </c>
       <c r="F12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G12" s="3">
         <v>2200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,23 +1239,26 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>55900</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>84500</v>
+      </c>
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1254,8 +1274,8 @@
       <c r="L14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1281,8 +1301,8 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>11</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>11</v>
@@ -1296,8 +1316,8 @@
       <c r="Z14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1305,8 +1325,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1375,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>11</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>11</v>
@@ -1370,26 +1393,29 @@
       <c r="W15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X15" s="3">
-        <v>300</v>
+      <c r="X15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Y15" s="3">
         <v>300</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>11</v>
+      <c r="Z15" s="3">
+        <v>300</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB15" s="3">
-        <v>400</v>
+      <c r="AB15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AC15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>169400</v>
+        <v>91100</v>
       </c>
       <c r="E17" s="3">
+        <v>198100</v>
+      </c>
+      <c r="F17" s="3">
         <v>56400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>80500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>57000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>81400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>89200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>77100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>72900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>79900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>68800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>51700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>41400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>50100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>56600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>45600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>32500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC17" s="3">
         <v>45400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>27800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-126800</v>
+        <v>-24000</v>
       </c>
       <c r="E18" s="3">
+        <v>-155500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,91 +1646,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12700</v>
+        <v>-3900</v>
       </c>
       <c r="E20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1761,91 +1798,94 @@
       <c r="W21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
       </c>
       <c r="F22" s="3">
+        <v>400</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1200</v>
       </c>
       <c r="J22" s="3">
         <v>1200</v>
       </c>
       <c r="K22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -1857,179 +1897,188 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-139900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-45800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-128300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-8400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-128200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5700</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12700</v>
+        <v>3900</v>
       </c>
       <c r="E32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-128200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5700</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-128200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5700</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42825</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,99 +3177,103 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E41" s="3">
         <v>89800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>91000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>96700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>103700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>128000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>44400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>11</v>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -3191,51 +3281,51 @@
       <c r="G42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="3">
         <v>11100</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="P42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>7000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>11</v>
       </c>
@@ -3245,103 +3335,109 @@
       <c r="Y42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1200</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E43" s="3">
         <v>67500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>71200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>93300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>128400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>192800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>171700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>171500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>170100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>154100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>140000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>148300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>149600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>139500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>130100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>78900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>69700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>65700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>69700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>42500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>30800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>29400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3423,230 +3519,239 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E45" s="3">
         <v>47400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>68400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>75800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>98100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>84700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>75600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>82400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>91000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>29200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>37500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E46" s="3">
         <v>204700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>216700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>245200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>295200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>351300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>353100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>350800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>352600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>321200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>326700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>229700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>244600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>245400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>209100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>155100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>149300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>151800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>117900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>124600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>127400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>90200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>85300</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3">
         <v>6200</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3">
         <v>12500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="3">
         <v>9100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O47" s="3">
         <v>3900</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1100</v>
-      </c>
-      <c r="S47" s="3">
-        <v>500</v>
       </c>
       <c r="T47" s="3">
         <v>500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>11</v>
+      <c r="U47" s="3">
+        <v>500</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>11</v>
@@ -3654,8 +3759,8 @@
       <c r="W47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3672,174 +3777,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3">
         <v>1500</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="3">
         <v>5800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>103200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>134600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>135400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>135800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>134700</v>
-      </c>
-      <c r="K49" s="3">
-        <v>130900</v>
       </c>
       <c r="L49" s="3">
         <v>130900</v>
       </c>
       <c r="M49" s="3">
+        <v>130900</v>
+      </c>
+      <c r="N49" s="3">
         <v>65700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>120900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>65700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>70100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>60900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>62100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>55700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>56000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>57000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>58100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>59100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>60100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>61200</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,91 +4121,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>36300</v>
       </c>
       <c r="F52" s="3">
         <v>36300</v>
       </c>
       <c r="G52" s="3">
+        <v>36300</v>
+      </c>
+      <c r="H52" s="3">
         <v>26800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>73000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>169900</v>
+      </c>
+      <c r="E54" s="3">
         <v>221800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>356200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>389400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>456700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>507700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>511900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>507400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>503400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>470100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>465400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>364300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>322000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>321500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>275500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>267100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>223200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>207300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>210000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>177000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>184700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>188800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>153000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>149400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC54" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,340 +4445,353 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E57" s="3">
         <v>41700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>66600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>71400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>46400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6600</v>
-      </c>
-      <c r="U57" s="3">
-        <v>4700</v>
       </c>
       <c r="V57" s="3">
         <v>4700</v>
       </c>
       <c r="W57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="X57" s="3">
         <v>4500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E58" s="3">
         <v>44300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>39100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>58900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>75500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>90300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>78600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>79400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>58100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>85900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>65800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>58400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>46200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>44300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>47600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>9600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E59" s="3">
         <v>51700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>58800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>64700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>59800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>63700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>60600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>63800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>51400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>46300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>41700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>45900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>51300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>111400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>112600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E60" s="3">
         <v>137700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>131400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>145200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>160300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>192100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>188100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>181600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>162800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>167400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>149300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>180100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>203900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>164000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>155400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>106900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>97200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>56900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>61200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>65700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>122300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>125800</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4730,91 +4873,97 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15300</v>
       </c>
       <c r="H62" s="3">
         <v>15300</v>
       </c>
       <c r="I62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J62" s="3">
         <v>22200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E66" s="3">
         <v>146900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>151800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>165600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>223400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>222900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>219400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>214000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>198000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>201700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>184200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>194200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>219400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>170800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>161500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>113800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>101900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>103200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>59500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>68800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>126000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>129800</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5411,22 +5579,25 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>89500</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>89300</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-422000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>232600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>251900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>299500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-221200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>306400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>305400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>300700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-207500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-208800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-202300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-202600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-190900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-185200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-186600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-183500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-181300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-173400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-151600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-149000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-148900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-140200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-146500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E76" s="3">
         <v>74900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>204400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>223900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>274500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>284400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>289000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>288000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>289400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>272100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>263700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>180000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>127800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>104700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>105500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>109400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>105300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>106900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>117500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>120600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>120000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-69700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42825</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-128200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5700</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6274,11 +6473,11 @@
         <v>0</v>
       </c>
       <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>11</v>
       </c>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,8 +6920,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6772,11 +6989,11 @@
         <v>0</v>
       </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>11</v>
       </c>
@@ -6789,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7040,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6888,8 +7109,8 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>11</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>11</v>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,8 +7296,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7135,11 +7365,11 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>11</v>
       </c>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,8 +7758,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7581,11 +7827,11 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>30600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>11</v>
       </c>
@@ -7598,8 +7844,11 @@
       <c r="AC100" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7664,11 +7913,11 @@
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>11</v>
       </c>
@@ -7681,8 +7930,11 @@
       <c r="AC101" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7747,11 +7999,11 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>11</v>
       </c>
@@ -7762,6 +8014,9 @@
         <v>11</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>11</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>ICLK</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E8" s="3">
         <v>67100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>42600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>47400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>76300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>86800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>78000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>66600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>78700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>68900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>58100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>54200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>49300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>39500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>42600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>42700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>39800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>29800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>25900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E9" s="3">
         <v>50400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>81200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>52800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>65100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>55400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>48800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>35800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>35800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>32800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>22900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E10" s="3">
         <v>16700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-38600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E12" s="3">
         <v>3300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2400</v>
       </c>
       <c r="F12" s="3">
         <v>2400</v>
       </c>
       <c r="G12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H12" s="3">
         <v>2200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,26 +1259,29 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>84500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1277,8 +1297,8 @@
       <c r="M14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1304,8 +1324,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>11</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>11</v>
@@ -1319,8 +1339,8 @@
       <c r="AA14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1378,8 +1401,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>11</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>11</v>
@@ -1396,26 +1419,29 @@
       <c r="X15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y15" s="3">
-        <v>300</v>
+      <c r="Y15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Z15" s="3">
         <v>300</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>11</v>
+      <c r="AA15" s="3">
+        <v>300</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC15" s="3">
-        <v>400</v>
+      <c r="AC15" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AD15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E17" s="3">
         <v>91100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>198100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>56400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>80500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>81400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>89200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>77100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>72900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>79900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>68800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>51700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>41400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>56600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>45600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>32500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD17" s="3">
         <v>45400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>27800</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-155500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-14000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,94 +1680,98 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1801,94 +1838,97 @@
       <c r="X21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
       </c>
       <c r="G22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1200</v>
       </c>
       <c r="K22" s="3">
         <v>1200</v>
       </c>
       <c r="L22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
-      </c>
-      <c r="V22" s="3">
-        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
@@ -1900,185 +1940,194 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-139900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-45800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-128300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-128200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-45100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5700</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-128200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5700</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-128200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5700</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,105 +3264,109 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E41" s="3">
         <v>73300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>91000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>103700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>44400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>11</v>
+      <c r="D42" s="3">
+        <v>300</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -3284,51 +3374,51 @@
       <c r="H42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="3">
         <v>11100</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="O42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R42" s="3">
         <v>400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>7000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>11</v>
       </c>
@@ -3338,106 +3428,112 @@
       <c r="Z42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB42" s="3">
         <v>1200</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E43" s="3">
         <v>50500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>93300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>128400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>192800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>171700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>171500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>170100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>154100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>140000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>148300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>149600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>139500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>130100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>78900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>69700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>65700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>69700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>42500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>30800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>29400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3522,239 +3618,248 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E45" s="3">
         <v>36300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>47400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>68400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>75800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>98100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>84700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>75600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>82400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>91000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>35800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>37500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>26500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>159800</v>
+      </c>
+      <c r="E46" s="3">
         <v>160000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>204700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>216700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>245200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>295200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>351300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>353100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>350800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>352600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>321200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>326700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>229700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>244600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>245400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>209100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>155100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>149300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>151800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>117900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>124600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>127400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>90200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>85300</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3">
         <v>6200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3">
         <v>12500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N47" s="3">
         <v>9100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P47" s="3">
         <v>3900</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R47" s="3">
         <v>1700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1100</v>
-      </c>
-      <c r="T47" s="3">
-        <v>500</v>
       </c>
       <c r="U47" s="3">
         <v>500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>11</v>
+      <c r="V47" s="3">
+        <v>500</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>11</v>
@@ -3762,8 +3867,8 @@
       <c r="X47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3780,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="3">
         <v>5800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P48" s="3">
         <v>1700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R48" s="3">
         <v>2200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1700</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>103200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>108000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>134600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>135400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>135800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>134700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>130900</v>
       </c>
       <c r="M49" s="3">
         <v>130900</v>
       </c>
       <c r="N49" s="3">
+        <v>130900</v>
+      </c>
+      <c r="O49" s="3">
         <v>65700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>120900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>65700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>70100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>60900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>62100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>55700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>56000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>57000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>58100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>59100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>60100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>61200</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>9100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>36300</v>
       </c>
       <c r="G52" s="3">
         <v>36300</v>
       </c>
       <c r="H52" s="3">
+        <v>36300</v>
+      </c>
+      <c r="I52" s="3">
         <v>26800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>73000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E54" s="3">
         <v>169900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>221800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>356200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>389400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>456700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>507700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>511900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>507400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>503400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>470100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>465400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>364300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>322000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>321500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>275500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>267100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>223200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>207300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>210000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>177000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>184700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>188800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>153000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>149400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,352 +4576,365 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E57" s="3">
         <v>34200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>66600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>57700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>71400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>66200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>46400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6600</v>
-      </c>
-      <c r="V57" s="3">
-        <v>4700</v>
       </c>
       <c r="W57" s="3">
         <v>4700</v>
       </c>
       <c r="X57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Y57" s="3">
         <v>4500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E58" s="3">
         <v>35200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>39100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>58900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>75500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>69700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>90300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>78600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>56000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>79400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>58100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>85900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>65800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>58400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>46200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>44300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9600</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E59" s="3">
         <v>46500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>51700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>60700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>64700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>59800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>63700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>66500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>51800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>63800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>46300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>45900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>51300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>111400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>112600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>120100</v>
+      </c>
+      <c r="E60" s="3">
         <v>115800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>137700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>131400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>145200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>160300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>192100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>188100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>181600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>162800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>167400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>149300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>180100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>203900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>164000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>155400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>106900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>97200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>100800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>56900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>61200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>65700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>122300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>125800</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4876,94 +5019,100 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>15300</v>
       </c>
       <c r="I62" s="3">
         <v>15300</v>
       </c>
       <c r="J62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K62" s="3">
         <v>22200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E66" s="3">
         <v>122800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>151800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>165600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>223400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>222900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>219400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>214000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>198000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>201700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>184200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>194200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>219400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>170800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>161500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>113800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>101900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>103200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>64100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>68800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>126000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>129800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5582,22 +5750,25 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>89500</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>89300</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-460700</v>
+      </c>
+      <c r="E72" s="3">
         <v>75500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-422000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>232600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>251900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>299500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-221200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>306400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>305400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>300700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-207500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-208800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-202300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-202600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-190900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-185200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-186600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-183500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-181300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-173400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-151600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-149000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-148900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-140200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-146500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E76" s="3">
         <v>47100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>204400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>223900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>274500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>284400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>289000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>288000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>289400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>272100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>263700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>180000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>127800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>102100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>104700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>105500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>109400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>105300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>106900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>117500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>120600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>120000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-62500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-69700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-128200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5700</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6476,11 +6675,11 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>11</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,8 +7137,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6992,11 +7209,11 @@
         <v>0</v>
       </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>11</v>
       </c>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7112,8 +7333,8 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>11</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>11</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,8 +7526,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7368,11 +7598,11 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>11</v>
       </c>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,8 +8004,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7830,11 +8076,11 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>30600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>11</v>
       </c>
@@ -7847,8 +8093,11 @@
       <c r="AD100" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7916,11 +8165,11 @@
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>11</v>
       </c>
@@ -7933,8 +8182,11 @@
       <c r="AD101" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8002,11 +8254,11 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>11</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>11</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>11</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICLK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>ICLK</t>
   </si>
@@ -656,403 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>66100</v>
+        <v>7100</v>
       </c>
       <c r="E8" s="3">
-        <v>67100</v>
+        <v>7100</v>
       </c>
       <c r="F8" s="3">
+        <v>33000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>33000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>33600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>33600</v>
+      </c>
+      <c r="J8" s="3">
         <v>42600</v>
       </c>
-      <c r="G8" s="3">
-        <v>41000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>38100</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>47400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>76300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>86800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>78000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>66600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>78700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>68900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>58100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>49000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>56700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>54200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>49300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>39200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>39500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>42600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>42700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>35200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>39800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>29800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>29900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>25900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>25400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>48000</v>
+        <v>3100</v>
       </c>
       <c r="E9" s="3">
-        <v>50400</v>
+        <v>3100</v>
       </c>
       <c r="F9" s="3">
-        <v>81200</v>
+        <v>23800</v>
       </c>
       <c r="G9" s="3">
-        <v>31800</v>
+        <v>23800</v>
       </c>
       <c r="H9" s="3">
-        <v>28800</v>
+        <v>25200</v>
       </c>
       <c r="I9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K9" s="3">
         <v>31400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>52800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>65100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>53700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>47000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>55400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>48800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>41500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>35800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>39500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>40600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>35800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>26800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>27800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>33300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>32800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>27100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>30000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>23300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>22900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>19500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>16200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>18100</v>
+        <v>4000</v>
       </c>
       <c r="E10" s="3">
-        <v>16700</v>
+        <v>4000</v>
       </c>
       <c r="F10" s="3">
-        <v>-38600</v>
+        <v>9200</v>
       </c>
       <c r="G10" s="3">
         <v>9200</v>
       </c>
       <c r="H10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K10" s="3">
+        <v>16000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>23500</v>
+      </c>
+      <c r="M10" s="3">
+        <v>21700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>24300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>19600</v>
+      </c>
+      <c r="P10" s="3">
+        <v>23300</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>20100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>16600</v>
+      </c>
+      <c r="S10" s="3">
+        <v>13200</v>
+      </c>
+      <c r="T10" s="3">
+        <v>17200</v>
+      </c>
+      <c r="U10" s="3">
+        <v>13600</v>
+      </c>
+      <c r="V10" s="3">
+        <v>13500</v>
+      </c>
+      <c r="W10" s="3">
+        <v>12400</v>
+      </c>
+      <c r="X10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Y10" s="3">
         <v>9300</v>
       </c>
-      <c r="I10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>23500</v>
-      </c>
-      <c r="K10" s="3">
-        <v>21700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>24300</v>
-      </c>
-      <c r="M10" s="3">
-        <v>19600</v>
-      </c>
-      <c r="N10" s="3">
-        <v>23300</v>
-      </c>
-      <c r="O10" s="3">
-        <v>20100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>16600</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>13200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>17200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>13600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>13500</v>
-      </c>
-      <c r="U10" s="3">
-        <v>12400</v>
-      </c>
-      <c r="V10" s="3">
-        <v>11700</v>
-      </c>
-      <c r="W10" s="3">
-        <v>9300</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>9900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>8100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>9800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>7000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>6400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>9200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1110,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4300</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
-        <v>3300</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="G12" s="3">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="H12" s="3">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="I12" s="3">
-        <v>2300</v>
+        <v>1600</v>
       </c>
       <c r="J12" s="3">
-        <v>3200</v>
+        <v>1500</v>
       </c>
       <c r="K12" s="3">
         <v>2300</v>
       </c>
       <c r="L12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N12" s="3">
         <v>2400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1100</v>
       </c>
       <c r="Q12" s="3">
         <v>1200</v>
       </c>
       <c r="R12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>2500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>5400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,31 +1296,37 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F14" s="3">
-        <v>84500</v>
+        <v>1800</v>
       </c>
       <c r="G14" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>24900</v>
+        <v>1800</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>11</v>
+      <c r="J14" s="3">
+        <v>126400</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>11</v>
@@ -1300,11 +1340,11 @@
       <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1327,11 +1367,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>11</v>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>11</v>
@@ -1342,40 +1382,46 @@
       <c r="AB14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1404,11 +1450,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>11</v>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>11</v>
@@ -1422,26 +1468,32 @@
       <c r="Y15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB15" s="3">
         <v>300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>300</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF15" s="3">
         <v>400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>84000</v>
+        <v>9300</v>
       </c>
       <c r="E17" s="3">
-        <v>91100</v>
+        <v>9300</v>
       </c>
       <c r="F17" s="3">
-        <v>198100</v>
+        <v>39900</v>
       </c>
       <c r="G17" s="3">
-        <v>56400</v>
+        <v>39900</v>
       </c>
       <c r="H17" s="3">
-        <v>80500</v>
+        <v>45500</v>
       </c>
       <c r="I17" s="3">
+        <v>45500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>64600</v>
+      </c>
+      <c r="K17" s="3">
         <v>57000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>81400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>89200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>77100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>72900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>79900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>68800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>56700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>51100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>62000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>56500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>51700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>41400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>50100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>56600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>43900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>37000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>45600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>32500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF17" s="3">
         <v>45400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>27800</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-17900</v>
+        <v>-2200</v>
       </c>
       <c r="E18" s="3">
-        <v>-24000</v>
+        <v>-2200</v>
       </c>
       <c r="F18" s="3">
-        <v>-155500</v>
+        <v>-6800</v>
       </c>
       <c r="G18" s="3">
-        <v>-15400</v>
+        <v>-6800</v>
       </c>
       <c r="H18" s="3">
-        <v>-42400</v>
+        <v>-12000</v>
       </c>
       <c r="I18" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-10600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-14000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,120 +1747,128 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>9000</v>
+        <v>-1300</v>
       </c>
       <c r="E20" s="3">
-        <v>-3900</v>
+        <v>-1300</v>
       </c>
       <c r="F20" s="3">
-        <v>16000</v>
+        <v>-3500</v>
       </c>
       <c r="G20" s="3">
         <v>-3500</v>
       </c>
       <c r="H20" s="3">
-        <v>-2700</v>
+        <v>2300</v>
       </c>
       <c r="I20" s="3">
-        <v>1200</v>
+        <v>2300</v>
       </c>
       <c r="J20" s="3">
-        <v>-400</v>
+        <v>-8400</v>
       </c>
       <c r="K20" s="3">
         <v>1200</v>
       </c>
       <c r="L20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-5900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-7000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>9100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>11</v>
+      <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-12600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>11</v>
@@ -1841,34 +1915,40 @@
       <c r="Y21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
@@ -1877,64 +1957,64 @@
         <v>400</v>
       </c>
       <c r="H22" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>900</v>
       </c>
       <c r="O22" s="3">
         <v>800</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>800</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
@@ -1943,191 +2023,209 @@
         <v>100</v>
       </c>
       <c r="AD22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9700</v>
+        <v>-600</v>
       </c>
       <c r="E23" s="3">
-        <v>-28500</v>
+        <v>-600</v>
       </c>
       <c r="F23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-139900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-19200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-45800</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-6100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-8500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-9200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-21100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>6300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
+        <v>300</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-11500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-10300</v>
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
-        <v>-28600</v>
+        <v>-600</v>
       </c>
       <c r="F26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-128300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-45800</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-8400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-21800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>6400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-18900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-10200</v>
+        <v>-3100</v>
       </c>
       <c r="E27" s="3">
-        <v>-28500</v>
+        <v>-3100</v>
       </c>
       <c r="F27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-128200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-45100</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-8600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-6600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-7900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-21800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>5700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,16 +2598,22 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2571,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-9000</v>
+        <v>1300</v>
       </c>
       <c r="E32" s="3">
-        <v>3900</v>
+        <v>1300</v>
       </c>
       <c r="F32" s="3">
-        <v>-16000</v>
+        <v>3500</v>
       </c>
       <c r="G32" s="3">
         <v>3500</v>
       </c>
       <c r="H32" s="3">
-        <v>2700</v>
+        <v>-2300</v>
       </c>
       <c r="I32" s="3">
-        <v>-1200</v>
+        <v>-2300</v>
       </c>
       <c r="J32" s="3">
-        <v>400</v>
+        <v>8400</v>
       </c>
       <c r="K32" s="3">
         <v>-1200</v>
       </c>
       <c r="L32" s="3">
+        <v>400</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>5900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>7000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-10200</v>
+        <v>-3100</v>
       </c>
       <c r="E33" s="3">
-        <v>-28500</v>
+        <v>-3100</v>
       </c>
       <c r="F33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-128200</v>
       </c>
-      <c r="G33" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-45100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-8600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-6600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-7900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-21800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>5700</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-10200</v>
+        <v>-3100</v>
       </c>
       <c r="E35" s="3">
-        <v>-28500</v>
+        <v>-3100</v>
       </c>
       <c r="F35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-128200</v>
       </c>
-      <c r="G35" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-45100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-8600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-6600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-7900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-21800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>5700</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,298 +3437,318 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>56500</v>
+        <v>70200</v>
       </c>
       <c r="E41" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="H41" s="3">
         <v>73300</v>
       </c>
-      <c r="F41" s="3">
-        <v>89800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>99900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>83500</v>
-      </c>
       <c r="I41" s="3">
+        <v>73300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>82800</v>
+      </c>
+      <c r="K41" s="3">
         <v>91000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>49200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>96700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>103700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>100200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>76000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>128000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>44300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>54000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>36900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>21100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>41900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>44700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>57300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>49800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>26100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>38300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>44400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>21900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>28200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>11</v>
+        <v>7300</v>
+      </c>
+      <c r="G42" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L42" s="3">
         <v>11100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P42" s="3">
         <v>100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T42" s="3">
         <v>400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>7000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD42" s="3">
         <v>1200</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>57800</v>
+        <v>11200</v>
       </c>
       <c r="E43" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>60900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>60900</v>
+      </c>
+      <c r="H43" s="3">
         <v>50500</v>
       </c>
-      <c r="F43" s="3">
-        <v>67500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>71200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>93300</v>
-      </c>
       <c r="I43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="J43" s="3">
+        <v>69700</v>
+      </c>
+      <c r="K43" s="3">
         <v>128400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>192800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>171700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>171500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>170100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>154100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>140000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>129200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>148300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>149600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>139500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>130100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>78900</v>
-      </c>
-      <c r="V43" s="3">
-        <v>69700</v>
-      </c>
-      <c r="W43" s="3">
-        <v>65700</v>
       </c>
       <c r="X43" s="3">
         <v>69700</v>
       </c>
       <c r="Y43" s="3">
+        <v>65700</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>69700</v>
+      </c>
+      <c r="AA43" s="3">
         <v>50500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>42500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>30800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>29400</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3621,260 +3813,278 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45300</v>
+        <v>70300</v>
       </c>
       <c r="E45" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H45" s="3">
         <v>36300</v>
       </c>
-      <c r="F45" s="3">
-        <v>47400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>45600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>68400</v>
-      </c>
       <c r="I45" s="3">
+        <v>36300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K45" s="3">
         <v>75800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>98100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>84700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>75600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>82400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>91000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>58700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>55700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>42300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>58600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>46700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>27800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>31600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>22300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>29200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>22100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>35800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>40500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>37500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>26500</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>151700</v>
+      </c>
+      <c r="F46" s="3">
         <v>159800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>159800</v>
+      </c>
+      <c r="H46" s="3">
         <v>160000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>160000</v>
+      </c>
+      <c r="J46" s="3">
         <v>204700</v>
       </c>
-      <c r="G46" s="3">
-        <v>216700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>245200</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>295200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>351300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>353100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>350800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>352600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>321200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>326700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>229700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>244600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>245400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>209100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>200000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>155100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>149300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>151800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>117900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>124600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>127400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>90200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>85300</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="3">
         <v>3400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3">
         <v>6200</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L47" s="3">
         <v>12500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P47" s="3">
         <v>9100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R47" s="3">
         <v>3900</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T47" s="3">
         <v>1700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3888,97 +4098,109 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P48" s="3">
         <v>4500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R48" s="3">
         <v>1700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T48" s="3">
         <v>2200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3986,88 +4208,94 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>700</v>
+      </c>
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="G49" s="3">
-        <v>103200</v>
-      </c>
-      <c r="H49" s="3">
-        <v>108000</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>134600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>135400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>135800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>134700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>130900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>130900</v>
-      </c>
-      <c r="O49" s="3">
-        <v>65700</v>
-      </c>
-      <c r="P49" s="3">
-        <v>120900</v>
       </c>
       <c r="Q49" s="3">
         <v>65700</v>
       </c>
       <c r="R49" s="3">
+        <v>120900</v>
+      </c>
+      <c r="S49" s="3">
+        <v>65700</v>
+      </c>
+      <c r="T49" s="3">
         <v>70100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>60900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>62100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>63200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>55700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>56000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>57000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>58100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>59100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>60100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>61200</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
+        <v>500</v>
+      </c>
+      <c r="H52" s="3">
         <v>9100</v>
       </c>
-      <c r="F52" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>36300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>36300</v>
-      </c>
       <c r="I52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>26800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>19900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>73000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>8100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>11700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1400</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1500</v>
       </c>
       <c r="V52" s="3">
         <v>1400</v>
       </c>
       <c r="W52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1200</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>155600</v>
+      </c>
+      <c r="F54" s="3">
         <v>163700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>163700</v>
+      </c>
+      <c r="H54" s="3">
         <v>169900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>169900</v>
+      </c>
+      <c r="J54" s="3">
         <v>221800</v>
       </c>
-      <c r="G54" s="3">
-        <v>356200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>389400</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>456700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>507700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>511900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>507400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>503400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>470100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>465400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>364300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>322000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>321500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>275500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>267100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>223200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>207300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>210000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>177000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>184700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>188800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>153000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>149400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,364 +4837,390 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
         <v>40300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>40300</v>
+      </c>
+      <c r="H57" s="3">
         <v>34200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>34200</v>
+      </c>
+      <c r="J57" s="3">
         <v>41700</v>
       </c>
-      <c r="G57" s="3">
-        <v>31600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>41300</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>44900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>66600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>57700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>37700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>43300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>43100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>27400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>36100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>71400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>66200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>46400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>33200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>9400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>6600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>4500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>3100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3600</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38400</v>
+        <v>36900</v>
       </c>
       <c r="E58" s="3">
+        <v>36900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>40100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>40100</v>
+      </c>
+      <c r="H58" s="3">
         <v>35200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
+        <v>35200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>46400</v>
+      </c>
+      <c r="K58" s="3">
+        <v>58900</v>
+      </c>
+      <c r="L58" s="3">
+        <v>75500</v>
+      </c>
+      <c r="M58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="N58" s="3">
+        <v>90300</v>
+      </c>
+      <c r="O58" s="3">
+        <v>78600</v>
+      </c>
+      <c r="P58" s="3">
+        <v>56000</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>79400</v>
+      </c>
+      <c r="R58" s="3">
+        <v>46600</v>
+      </c>
+      <c r="S58" s="3">
+        <v>58100</v>
+      </c>
+      <c r="T58" s="3">
+        <v>85900</v>
+      </c>
+      <c r="U58" s="3">
+        <v>65800</v>
+      </c>
+      <c r="V58" s="3">
+        <v>58400</v>
+      </c>
+      <c r="W58" s="3">
+        <v>46200</v>
+      </c>
+      <c r="X58" s="3">
         <v>44300</v>
       </c>
-      <c r="G58" s="3">
-        <v>39100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>45100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>58900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>75500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>69700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>90300</v>
-      </c>
-      <c r="M58" s="3">
-        <v>78600</v>
-      </c>
-      <c r="N58" s="3">
-        <v>56000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>79400</v>
-      </c>
-      <c r="P58" s="3">
-        <v>46600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>58100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>85900</v>
-      </c>
-      <c r="S58" s="3">
-        <v>65800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>58400</v>
-      </c>
-      <c r="U58" s="3">
-        <v>46200</v>
-      </c>
-      <c r="V58" s="3">
-        <v>44300</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>47600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>10400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>10800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>10500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>7800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>9600</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41300</v>
+        <v>80400</v>
       </c>
       <c r="E59" s="3">
+        <v>80400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>15700</v>
+      </c>
+      <c r="H59" s="3">
         <v>46500</v>
       </c>
-      <c r="F59" s="3">
-        <v>51700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>60700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>58800</v>
-      </c>
       <c r="I59" s="3">
+        <v>46500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K59" s="3">
         <v>56500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>58700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>64700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>60100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>59800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>63700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>60600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>66500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>50600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>51900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>51800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>63800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>51400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>46300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>48500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>41700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>45900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>51300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>111400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>112600</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>120700</v>
+      </c>
+      <c r="F60" s="3">
         <v>120100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>120100</v>
+      </c>
+      <c r="H60" s="3">
         <v>115800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>115800</v>
+      </c>
+      <c r="J60" s="3">
         <v>137700</v>
       </c>
-      <c r="G60" s="3">
-        <v>131400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>145200</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>160300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>200800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>192100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>188100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>181600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>162800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>167400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>149300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>180100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>203900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>164000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>155400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>106900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>97200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>100800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>56900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>61200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>65700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>122300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>125800</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4945,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4957,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5022,97 +5308,109 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="L62" s="3">
+        <v>15300</v>
+      </c>
+      <c r="M62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="N62" s="3">
+        <v>22700</v>
+      </c>
+      <c r="O62" s="3">
+        <v>25800</v>
+      </c>
+      <c r="P62" s="3">
+        <v>28200</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>15500</v>
+      </c>
+      <c r="R62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="S62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="U62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X62" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Y62" s="3">
         <v>2400</v>
       </c>
-      <c r="E62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>14500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>15300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>22200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>22700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>25800</v>
-      </c>
-      <c r="N62" s="3">
-        <v>28200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>15500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>15600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="R62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="U62" s="3">
-        <v>4600</v>
-      </c>
-      <c r="V62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="W62" s="3">
-        <v>2400</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3900</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>126600</v>
+        <v>122400</v>
       </c>
       <c r="E66" s="3">
-        <v>122800</v>
+        <v>122400</v>
       </c>
       <c r="F66" s="3">
-        <v>146900</v>
+        <v>122500</v>
       </c>
       <c r="G66" s="3">
-        <v>151800</v>
+        <v>122500</v>
       </c>
       <c r="H66" s="3">
-        <v>165600</v>
+        <v>118500</v>
       </c>
       <c r="I66" s="3">
+        <v>118500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>142500</v>
+      </c>
+      <c r="K66" s="3">
         <v>182200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>223400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>222900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>219400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>214000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>198000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>201700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>184200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>194200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>219400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>170800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>161500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>113800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>101900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>103200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>59500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>64100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>68800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>126000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>129800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5753,22 +6089,28 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>89500</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>89300</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="3">
         <v>-460700</v>
       </c>
-      <c r="E72" s="3">
-        <v>75500</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-460700</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J72" s="3">
         <v>-422000</v>
       </c>
-      <c r="G72" s="3">
-        <v>232600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>251900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>299500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-221200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>306400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>305400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>300700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-207500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-208800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-202300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-202600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-190900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-185200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-186600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-183500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-181300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-173400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-151600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-149000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-148900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-140200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-146500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F76" s="3">
         <v>37100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>37100</v>
+      </c>
+      <c r="H76" s="3">
         <v>47100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>47100</v>
+      </c>
+      <c r="J76" s="3">
         <v>74900</v>
       </c>
-      <c r="G76" s="3">
-        <v>204400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>223900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>274500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>284400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>289000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>288000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>289400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>272100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>263700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>180000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>127800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>102100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>104700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>105500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>109400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>105300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>106900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>117500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>120600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>120000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-62500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-69700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-10200</v>
+        <v>-3100</v>
       </c>
       <c r="E81" s="3">
-        <v>-28500</v>
+        <v>-3100</v>
       </c>
       <c r="F81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-128200</v>
       </c>
-      <c r="G81" s="3">
-        <v>-19000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-45100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-8600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-6600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-7900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-21800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>5700</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,31 +7002,33 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6678,14 +7076,14 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1400</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>11</v>
       </c>
@@ -6695,8 +7093,14 @@
       <c r="AE83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,31 +7568,37 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7212,14 +7646,14 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>11</v>
       </c>
@@ -7229,8 +7663,14 @@
       <c r="AE89" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,31 +7702,33 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7336,11 +7778,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>11</v>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>11</v>
@@ -7351,8 +7793,14 @@
       <c r="AE91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,31 +7983,37 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7601,14 +8061,14 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>11</v>
       </c>
@@ -7618,8 +8078,14 @@
       <c r="AE94" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,31 +8117,33 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7740,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,31 +8493,37 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8079,14 +8571,14 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>30600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>11</v>
       </c>
@@ -8096,31 +8588,37 @@
       <c r="AE100" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8168,14 +8666,14 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>11</v>
       </c>
@@ -8185,31 +8683,37 @@
       <c r="AE101" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8257,14 +8761,14 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>11</v>
       </c>
@@ -8272,6 +8776,12 @@
         <v>11</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>11</v>
       </c>
     </row>
